--- a/docs/FunCollection/FunCollection_8.xlsx
+++ b/docs/FunCollection/FunCollection_8.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="246">
   <si>
     <t>temp_01</t>
   </si>
@@ -630,6 +630,138 @@
   </si>
   <si>
     <t>/global_reward/Fun13/Fun13_FunCollection_8_CL_10_2.proto.js</t>
+  </si>
+  <si>
+    <t>identifier</t>
+  </si>
+  <si>
+    <t>ingredients</t>
+  </si>
+  <si>
+    <t>\recipe\BD24\BD24_Swap_R_1_Recipe.proto.js</t>
+  </si>
+  <si>
+    <t>Рецепты FunCollection_8</t>
+  </si>
+  <si>
+    <t>Fun13_FunCollection_8_CL_1_Recipe</t>
+  </si>
+  <si>
+    <t>Fun13_FunCollection_8_CL_2_Recipe</t>
+  </si>
+  <si>
+    <t>Fun13_FunCollection_8_CL_3_Recipe</t>
+  </si>
+  <si>
+    <t>Fun13_FunCollection_8_CL_4_Recipe</t>
+  </si>
+  <si>
+    <t>Fun13_FunCollection_8_CL_5_Recipe</t>
+  </si>
+  <si>
+    <t>Fun13_FunCollection_8_CL_6_Recipe</t>
+  </si>
+  <si>
+    <t>Fun13_FunCollection_8_CL_7_Recipe</t>
+  </si>
+  <si>
+    <t>Fun13_FunCollection_8_CL_8_Recipe</t>
+  </si>
+  <si>
+    <t>Fun13_FunCollection_8_CL_9_Recipe</t>
+  </si>
+  <si>
+    <t>Fun13_FunCollection_8_CL_10_Recipe</t>
+  </si>
+  <si>
+    <t>/recipe/Fun/Fun13/Fun13_FunCollection_8_CL_1_Recipe.proto.js</t>
+  </si>
+  <si>
+    <t>/recipe/Fun/Fun13/Fun13_FunCollection_8_CL_2_Recipe.proto.js</t>
+  </si>
+  <si>
+    <t>/recipe/Fun/Fun13/Fun13_FunCollection_8_CL_3_Recipe.proto.js</t>
+  </si>
+  <si>
+    <t>/recipe/Fun/Fun13/Fun13_FunCollection_8_CL_4_Recipe.proto.js</t>
+  </si>
+  <si>
+    <t>/recipe/Fun/Fun13/Fun13_FunCollection_8_CL_5_Recipe.proto.js</t>
+  </si>
+  <si>
+    <t>/recipe/Fun/Fun13/Fun13_FunCollection_8_CL_6_Recipe.proto.js</t>
+  </si>
+  <si>
+    <t>/recipe/Fun/Fun13/Fun13_FunCollection_8_CL_8_Recipe.proto.js</t>
+  </si>
+  <si>
+    <t>/recipe/Fun/Fun13/Fun13_FunCollection_8_CL_7_Recipe.proto.js</t>
+  </si>
+  <si>
+    <t>/recipe/Fun/Fun13/Fun13_FunCollection_8_CL_9_Recipe.proto.js</t>
+  </si>
+  <si>
+    <t>/recipe/Fun/Fun13/Fun13_FunCollection_8_CL_10_Recipe.proto.js</t>
+  </si>
+  <si>
+    <t>asset=Fun13_FunCollection_8_CL_1:1</t>
+  </si>
+  <si>
+    <t>asset=Fun13_FunCollection_8_CL_2:1</t>
+  </si>
+  <si>
+    <t>asset=Fun13_FunCollection_8_CL_3:1</t>
+  </si>
+  <si>
+    <t>asset=Fun13_FunCollection_8_CL_4:1</t>
+  </si>
+  <si>
+    <t>asset=Fun13_FunCollection_8_CL_5:1</t>
+  </si>
+  <si>
+    <t>asset=Fun13_FunCollection_8_CL_6:1</t>
+  </si>
+  <si>
+    <t>asset=Fun13_FunCollection_8_CL_7:1</t>
+  </si>
+  <si>
+    <t>asset=Fun13_FunCollection_8_CL_8:1</t>
+  </si>
+  <si>
+    <t>asset=Fun13_FunCollection_8_CL_9:1</t>
+  </si>
+  <si>
+    <t>asset=Fun13_FunCollection_8_CL_10:1</t>
+  </si>
+  <si>
+    <t>asset=Fun13_FunCollection_8_CL_1_1:1+asset=Fun13_FunCollection_8_CL_1_2:1</t>
+  </si>
+  <si>
+    <t>asset=Fun13_FunCollection_8_CL_2_1:1+asset=Fun13_FunCollection_8_CL_2_2:1</t>
+  </si>
+  <si>
+    <t>asset=Fun13_FunCollection_8_CL_3_1:1+asset=Fun13_FunCollection_8_CL_3_2:1</t>
+  </si>
+  <si>
+    <t>asset=Fun13_FunCollection_8_CL_4_1:1+asset=Fun13_FunCollection_8_CL_4_2:1</t>
+  </si>
+  <si>
+    <t>asset=Fun13_FunCollection_8_CL_5_1:1+asset=Fun13_FunCollection_8_CL_5_2:1</t>
+  </si>
+  <si>
+    <t>asset=Fun13_FunCollection_8_CL_6_1:1+asset=Fun13_FunCollection_8_CL_6_2:1</t>
+  </si>
+  <si>
+    <t>asset=Fun13_FunCollection_8_CL_7_1:1+asset=Fun13_FunCollection_8_CL_7_2:1</t>
+  </si>
+  <si>
+    <t>asset=Fun13_FunCollection_8_CL_8_1:1+asset=Fun13_FunCollection_8_CL_8_2:1</t>
+  </si>
+  <si>
+    <t>asset=Fun13_FunCollection_8_CL_9_1:1+asset=Fun13_FunCollection_8_CL_9_2:1</t>
+  </si>
+  <si>
+    <t>asset=Fun13_FunCollection_8_CL_10_1:1+asset=Fun13_FunCollection_8_CL_10_2:1</t>
   </si>
 </sst>
 </file>
@@ -702,7 +834,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -725,6 +857,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1006,7 +1150,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:Q88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="38.5703125" customWidth="1"/>
@@ -2469,7 +2613,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>64</v>
       </c>
@@ -2495,7 +2639,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>64</v>
       </c>
@@ -2521,7 +2665,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>64</v>
       </c>
@@ -2547,7 +2691,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>64</v>
       </c>
@@ -2573,7 +2717,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>64</v>
       </c>
@@ -2599,12 +2743,12 @@
         <v>88</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>0</v>
       </c>
@@ -2633,7 +2777,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>6</v>
       </c>
@@ -2659,7 +2803,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>69</v>
       </c>
@@ -2680,6 +2824,286 @@
       </c>
       <c r="H74" t="s">
         <v>99</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="11"/>
+      <c r="B76" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="C76" s="11"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="11"/>
+      <c r="I76" s="11"/>
+      <c r="J76" s="11"/>
+      <c r="K76" s="11"/>
+      <c r="L76" s="11"/>
+    </row>
+    <row r="77" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B77" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E77" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F77" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="G77" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="H77" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="I77" s="11"/>
+      <c r="J77" s="11"/>
+      <c r="K77" s="11"/>
+      <c r="L77" s="11"/>
+    </row>
+    <row r="78" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="11"/>
+      <c r="B78" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F78" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="G78" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H78" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I78" s="11"/>
+      <c r="J78" s="11"/>
+      <c r="K78" s="11"/>
+      <c r="L78" s="11"/>
+    </row>
+    <row r="79" spans="1:12" s="6" customFormat="1" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="A79" s="11"/>
+      <c r="B79" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="E79" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="F79" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="G79" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="H79" s="11"/>
+      <c r="I79" s="11"/>
+      <c r="J79" s="11"/>
+      <c r="K79" s="11"/>
+      <c r="L79" s="11"/>
+    </row>
+    <row r="80" spans="1:12" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="B80" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="E80" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="F80" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="G80" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="2:7" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="B81" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="D81" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="E81" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="F81" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="G81" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="B82" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="E82" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="F82" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="G82" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="B83" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="E83" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="F83" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="G83" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="B84" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="E84" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="F84" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="G84" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="B85" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="D85" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E85" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="F85" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="G85" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="B86" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D86" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E86" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="F86" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="G86" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="B87" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="D87" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="E87" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="F87" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="G87" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="B88" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D88" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="E88" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="F88" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="G88" s="14" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
